--- a/AAII_Financials/Yearly/NRDE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NRDE_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="92">
   <si>
     <t>NRDE</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -921,7 +921,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>259700</v>
+        <v>351200</v>
       </c>
       <c r="E17" s="3">
         <v>387500</v>
@@ -948,7 +948,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-257300</v>
+        <v>-348900</v>
       </c>
       <c r="E18" s="3">
         <v>-387300</v>
@@ -988,7 +988,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-85700</v>
+        <v>5800</v>
       </c>
       <c r="E20" s="3">
         <v>104900</v>
@@ -1149,8 +1149,8 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>3</v>
+      <c r="D26" s="3">
+        <v>-343100</v>
       </c>
       <c r="E26" s="3">
         <v>-282400</v>
@@ -1176,8 +1176,8 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>3</v>
+      <c r="D27" s="3">
+        <v>-345600</v>
       </c>
       <c r="E27" s="3">
         <v>-282700</v>
@@ -1312,7 +1312,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>85700</v>
+        <v>-5800</v>
       </c>
       <c r="E32" s="3">
         <v>-104900</v>
@@ -1338,8 +1338,8 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>3</v>
+      <c r="D33" s="3">
+        <v>-345600</v>
       </c>
       <c r="E33" s="3">
         <v>-282700</v>
@@ -1392,8 +1392,8 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>3</v>
+      <c r="D35" s="3">
+        <v>-345600</v>
       </c>
       <c r="E35" s="3">
         <v>-282700</v>
@@ -1504,8 +1504,8 @@
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>3</v>
+      <c r="D42" s="3">
+        <v>0</v>
       </c>
       <c r="E42" s="3">
         <v>100300</v>
@@ -1558,8 +1558,8 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>3</v>
+      <c r="D44" s="3">
+        <v>0</v>
       </c>
       <c r="E44" s="3">
         <v>13700</v>
@@ -1666,8 +1666,8 @@
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>3</v>
+      <c r="D48" s="3">
+        <v>0</v>
       </c>
       <c r="E48" s="3">
         <v>193800</v>
@@ -1882,7 +1882,7 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>15400</v>
+        <v>13700</v>
       </c>
       <c r="E57" s="3">
         <v>12800</v>
@@ -1935,8 +1935,8 @@
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>3</v>
+      <c r="D59" s="3">
+        <v>1600</v>
       </c>
       <c r="E59" s="3">
         <v>56000</v>
@@ -2381,7 +2381,7 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>-19300</v>
+        <v>13500</v>
       </c>
       <c r="E76" s="3">
         <v>351700</v>
@@ -2466,8 +2466,8 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>3</v>
+      <c r="D81" s="3">
+        <v>-345600</v>
       </c>
       <c r="E81" s="3">
         <v>-282700</v>
@@ -2937,8 +2937,8 @@
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
+      <c r="D100" s="3">
+        <v>0</v>
       </c>
       <c r="E100" s="3">
         <v>206000</v>
